--- a/users.xlsx
+++ b/users.xlsx
@@ -1,34 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BOT\pt3bot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE027447-C8D9-4C36-B860-CFE9677E88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="users" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>nik</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>password_hash</t>
+  </si>
+  <si>
+    <t>role</t>
+  </si>
+  <si>
+    <t>project</t>
+  </si>
+  <si>
+    <t>10000001</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>developer</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>scrypt:32768:8:1:$dKXuRVEyPUsp/QQI$6f7f8acb63b1a71a656088d40312cb499406288d1b52a3be32a75035e373716690d57f2f4bf0e4159ee5356803e7e221e9a134b9d1dd39005f34b71c1ad92a7e</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +91,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,66 +393,45 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="161.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>nik</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>password_hash</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>project</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>scrypt:32768:8:1$puhmZlGd64rN4FTY$d7acb4457fe8d93dbc6f0183ea152b3b3dc222c840d275428d4c5c86429aeb297b6a9ff018035fc587fb97524aa989e51236e3f4aac0cb7c410ad441e969dc47</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>developer</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -1,78 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BOT\pt3bot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE027447-C8D9-4C36-B860-CFE9677E88D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="users" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>nik</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>password_hash</t>
-  </si>
-  <si>
-    <t>role</t>
-  </si>
-  <si>
-    <t>project</t>
-  </si>
-  <si>
-    <t>10000001</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>developer</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>scrypt:32768:8:1:$dKXuRVEyPUsp/QQI$6f7f8acb63b1a71a656088d40312cb499406288d1b52a3be32a75035e373716690d57f2f4bf0e4159ee5356803e7e221e9a134b9d1dd39005f34b71c1ad92a7e</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -91,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -393,45 +407,69 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="161.109375" bestFit="1" customWidth="1"/>
+    <col width="161.109375" bestFit="1" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>nik</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>password_hash</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$dKXuRVEyPUsp/QQI$6f7f8acb63b1a71a656088d40312cb499406288d1b52a3be32a75035e373716690d57f2f4bf0e4159ee5356803e7e221e9a134b9d1dd39005f34b71c1ad92a7e</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>developer</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/users.xlsx
+++ b/users.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$dKXuRVEyPUsp/QQI$6f7f8acb63b1a71a656088d40312cb499406288d1b52a3be32a75035e373716690d57f2f4bf0e4159ee5356803e7e221e9a134b9d1dd39005f34b71c1ad92a7e</t>
+          <t>scrypt:32768:8:1$qajnxX75get14j3T$998d257ea704785df7123d1bfbdca09878adf26a13eb429e92b6a718108faf8e257e58b1b75346b67f48237b45a44238adb9f064810dfb525d70311690ff6f51</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/users.xlsx
+++ b/users.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,10 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="161.109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,15 +463,69 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>scrypt:32768:8:1$qajnxX75get14j3T$998d257ea704785df7123d1bfbdca09878adf26a13eb429e92b6a718108faf8e257e58b1b75346b67f48237b45a44238adb9f064810dfb525d70311690ff6f51</t>
+          <t>scrypt:32768:8:1$YvC835gbNk6xd9sy$87f7fc4a0d8cb59f5c542e89ac603d838d252c68f2fd6326e5430d83d72f5b14adcc944f6c64a095376656b274a90e103817db17fdaa2980e7adc22b19b98fcd</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$Awop6owzwcxDsIry$805a02a3c6baf4e1c45ebe4c4d06f59aa33587657e95c48bb43bccf759596cae189f7631a78c0ec91d23916d0326a201baf66c041176ce49644cdabeb2e3e5db</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>developer</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>90000001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tsel</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>scrypt:32768:8:1$WkcVTPGf6uD3Q0Gn$17e9982d99fd4b48e8e984e1e63b746bc225d8bafeee9b692bcf140e57bd1bdab03f3348e0cfd1c0c74c4ec4f7335bc7c8adb91aa825a51b939131281cba3e4f</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>viewer</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
